--- a/Apostas_Diarias/Apostas_20260422.xlsx
+++ b/Apostas_Diarias/Apostas_20260422.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F9526CF0F1583DFF0505370F66261E289" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7759969-91E1-4009-BC7B-ABB465F88476}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F95564AE06EB990905A1510344D07F763" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E50AF746-608D-426C-8E35-4F73E9FE1534}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Data</t>
   </si>
@@ -74,33 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Oliveirense x Benfica B</t>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>ICELAND 1</t>
+  </si>
+  <si>
+    <t>Keflavik x Breidablik</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>ICELAND 1</t>
-  </si>
-  <si>
-    <t>Keflavik x Breidablik</t>
-  </si>
-  <si>
-    <t>SPAIN 1</t>
-  </si>
-  <si>
-    <t>Real Sociedad x Getafe</t>
-  </si>
-  <si>
     <t>15:30:00</t>
   </si>
   <si>
@@ -108,27 +93,6 @@
   </si>
   <si>
     <t>Sturm Graz x LASK Linz</t>
-  </si>
-  <si>
-    <t>20:30:00</t>
-  </si>
-  <si>
-    <t>USA 1</t>
-  </si>
-  <si>
-    <t>Toronto FC x Philadelphia</t>
-  </si>
-  <si>
-    <t>23:00:00</t>
-  </si>
-  <si>
-    <t>Oakland Roots x Las Vegas Lights FC</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>Lay_CS_1x0_B365</t>
   </si>
 </sst>
 </file>
@@ -468,14 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="39" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -527,13 +491,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -567,282 +531,39 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J9" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f>IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K9" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>31.166666666666668</v>
+        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>42.5</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4">
-        <v>10.5</v>
-      </c>
-      <c r="H4">
-        <v>10.5</v>
-      </c>
-      <c r="I4">
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>12.5</v>
-      </c>
-      <c r="H8">
-        <v>12.5</v>
-      </c>
-      <c r="I8">
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9">
-        <v>11.5</v>
-      </c>
-      <c r="H9">
-        <v>11.5</v>
-      </c>
-      <c r="I9">
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K9">
-    <sortCondition ref="E2:E9"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Apostas_Diarias/Apostas_20260422.xlsx
+++ b/Apostas_Diarias/Apostas_20260422.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F95564AE06EB990905A1510344D07F763" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E50AF746-608D-426C-8E35-4F73E9FE1534}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9536CD023D60CAF0505CA8754CC1F47D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51ECB451-4575-4A73-9FB6-E73F119DBDA6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>Data</t>
   </si>
@@ -74,25 +74,31 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>ICELAND 1</t>
-  </si>
-  <si>
-    <t>Keflavik x Breidablik</t>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>CHINA 1</t>
+  </si>
+  <si>
+    <t>Qingdao Youth Island x Henan Songshan Longmen</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>AUSTRIA 1</t>
-  </si>
-  <si>
-    <t>Sturm Graz x LASK Linz</t>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica x FK Novi Pazar</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>Zeleznicar Pancevo x Crvena Zvezda</t>
   </si>
 </sst>
 </file>
@@ -432,14 +438,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -482,6 +487,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -503,12 +511,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="H2">
-        <v>14.5</v>
+        <f>G2</f>
+        <v>11.5</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -517,7 +527,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>34.629629629629626</v>
+        <v>44.523809523809526</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -543,23 +553,67 @@
         <v>16</v>
       </c>
       <c r="G3">
+        <v>11.5</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H4" si="0">G3</f>
+        <v>11.5</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="1">$L$1</f>
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="H3">
-        <v>12</v>
-      </c>
-      <c r="I3">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>11.5</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="J3" t="str">
-        <f>IF(L3=1,"GREEN","RED")</f>
+      <c r="J4" t="str">
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
-      <c r="K3">
-        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>42.5</v>
-      </c>
-      <c r="L3">
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260422.xlsx
+++ b/Apostas_Diarias/Apostas_20260422.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9536CD023D60CAF0505CA8754CC1F47D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51ECB451-4575-4A73-9FB6-E73F119DBDA6}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F95564AE06EB990905A1510344D07F763" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E50AF746-608D-426C-8E35-4F73E9FE1534}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Data</t>
   </si>
@@ -74,31 +74,25 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>08:35:00</t>
-  </si>
-  <si>
-    <t>CHINA 1</t>
-  </si>
-  <si>
-    <t>Qingdao Youth Island x Henan Songshan Longmen</t>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>ICELAND 1</t>
+  </si>
+  <si>
+    <t>Keflavik x Breidablik</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica x FK Novi Pazar</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>Zeleznicar Pancevo x Crvena Zvezda</t>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>AUSTRIA 1</t>
+  </si>
+  <si>
+    <t>Sturm Graz x LASK Linz</t>
   </si>
 </sst>
 </file>
@@ -438,13 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -487,9 +482,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -511,14 +503,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -527,7 +517,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>44.523809523809526</v>
+        <v>34.629629629629626</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -553,67 +543,23 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H4" si="0">G3</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I4" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f>IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>44.523809523809526</v>
+        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>42.5</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>11.5</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
